--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rfdd2b73eee904e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rc34cb1df0ca74fee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -214,7 +214,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -224,7 +224,7 @@
         <x:color rgb="FFA12828"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
         </x:patternFill>
       </x:fill>
@@ -464,7 +464,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>只允许下列七类内容。当前仅表示本地材料准备情况，不代表已上传、已批准或平台检索已通过。</x:v>
+        <x:v>七类独立导入文件已准备；知识库空对象已创建。当前仍为0文件、未上传、未索引，不代表平台检索或A复核通过。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -532,28 +532,34 @@
         <x:v>模型交接与字段字典</x:v>
       </x:c>
       <x:c r="C5" s="20" t="str">
-        <x:v>../../00_共享/模型交接/MODEL_HANDOFF_V50.txt；FIELD_DICTIONARY_V50.xlsx</x:v>
+        <x:v>KB_UPLOAD_READY/01_模型与字段绑定说明_V50.md</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
-        <x:v>模型名、表字段、类型、粒度、空值与所有者</x:v>
+        <x:v>固定模型、22张表、最小字段域、版本冲突和已知缺口</x:v>
       </x:c>
       <x:c r="E5" s="20" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>待A补最终冻结修订号并只读复核</x:v>
-      </x:c>
-      <x:c r="G5" s="20" t="str"/>
-      <x:c r="H5" s="20" t="str"/>
-      <x:c r="I5" s="20" t="str"/>
+        <x:v>UPSTREAM_SIGN_PENDING / A最终冻结与签收待补</x:v>
+      </x:c>
+      <x:c r="G5" s="20" t="str">
+        <x:v>V50-KB01-LOCAL_READY-r1</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="str">
+        <x:v>446bd1a988c10e82418919a86256423fb74772d7aea212a7224db7d3008db088</x:v>
+      </x:c>
+      <x:c r="I5" s="20" t="str">
+        <x:v>01_模型与字段绑定说明_V50.md</x:v>
+      </x:c>
       <x:c r="J5" s="20" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K5" s="20" t="str"/>
-      <x:c r="L5" s="20" t="str"/>
-      <x:c r="M5" s="20" t="str"/>
+      <x:c r="K5" s="20"/>
+      <x:c r="L5" s="20"/>
+      <x:c r="M5" s="20"/>
       <x:c r="N5" s="20" t="str">
-        <x:v>MODEL_HANDOFF 仍为 V5.0-A04-DRAFT-r3</x:v>
+        <x:v>文件已可上传；不得写成A04最终冻结或上游已批准</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -564,7 +570,7 @@
         <x:v>指标公式、空值和日期口径</x:v>
       </x:c>
       <x:c r="C6" s="21" t="str">
-        <x:v>../01_知识库与边界/05_KB知识库7类内容骨架.md#第-2-类指标公式空值和日期口径-</x:v>
+        <x:v>KB_UPLOAD_READY/02_指标公式空值日期口径_V50.md</x:v>
       </x:c>
       <x:c r="D6" s="21" t="str">
         <x:v>汇率/CPI/ODI/储备/组合公式；缺失不补0；独立截止期</x:v>
@@ -573,19 +579,25 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F6" s="21" t="str">
-        <x:v>待平台上传后A只读复核</x:v>
-      </x:c>
-      <x:c r="G6" s="21" t="str"/>
-      <x:c r="H6" s="21" t="str"/>
-      <x:c r="I6" s="21" t="str"/>
+        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+      </x:c>
+      <x:c r="G6" s="21" t="str">
+        <x:v>V50-KB02-LOCAL_FINAL-r1</x:v>
+      </x:c>
+      <x:c r="H6" s="21" t="str">
+        <x:v>0fa0f8359ccf6135a1605a6809136da846e4d5d0908818fbdd2ea3c71b6147fe</x:v>
+      </x:c>
+      <x:c r="I6" s="21" t="str">
+        <x:v>02_指标公式空值日期口径_V50.md</x:v>
+      </x:c>
       <x:c r="J6" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K6" s="21" t="str"/>
-      <x:c r="L6" s="21" t="str"/>
-      <x:c r="M6" s="21" t="str"/>
+      <x:c r="K6" s="21"/>
+      <x:c r="L6" s="21"/>
+      <x:c r="M6" s="21"/>
       <x:c r="N6" s="21" t="str">
-        <x:v>不得把本地定稿等同平台批准</x:v>
+        <x:v>B自有内容本地定稿；平台上传和检索尚未开始</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" customHeight="1">
@@ -596,28 +608,34 @@
         <x:v>六页页面说明</x:v>
       </x:c>
       <x:c r="C7" s="21" t="str">
-        <x:v>DB01—DB06当前手册与组件映射</x:v>
+        <x:v>KB_UPLOAD_READY/03_六页页面说明_V50.md</x:v>
       </x:c>
       <x:c r="D7" s="21" t="str">
-        <x:v>每页回答问题、组件、筛选、联动和边界</x:v>
+        <x:v>DB01—DB06问题、组件、筛选、联动、当前证据边界</x:v>
       </x:c>
       <x:c r="E7" s="21" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>待六页证据闭环后A只读复核</x:v>
-      </x:c>
-      <x:c r="G7" s="21" t="str"/>
-      <x:c r="H7" s="21" t="str"/>
-      <x:c r="I7" s="21" t="str"/>
+        <x:v>PAGE_EVIDENCE_AND_G3_SIGN_PENDING</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="str">
+        <x:v>V50-KB03-LOCAL_READY-r2</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="str">
+        <x:v>3452c3fbcde1cd6589fe05f655cd9a8f91c3d90c7ce32b0b76f8649f21591c07</x:v>
+      </x:c>
+      <x:c r="I7" s="21" t="str">
+        <x:v>03_六页页面说明_V50.md</x:v>
+      </x:c>
       <x:c r="J7" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K7" s="21" t="str"/>
-      <x:c r="L7" s="21" t="str"/>
-      <x:c r="M7" s="21" t="str"/>
+      <x:c r="K7" s="21"/>
+      <x:c r="L7" s="21"/>
+      <x:c r="M7" s="21"/>
       <x:c r="N7" s="21" t="str">
-        <x:v>DB03完整手册待同步；DB04未完成；G3仍BLOCKED</x:v>
+        <x:v>DB01/DB02 B复核通过、DB06正式PASS；DB04格式收口/B正式复核与G3待完成</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
@@ -628,28 +646,34 @@
         <x:v>source_id追溯规则</x:v>
       </x:c>
       <x:c r="C8" s="21" t="str">
-        <x:v>../01_知识库与边界/05_KB知识库7类内容骨架.md#第-4-类source_id-追溯规则-</x:v>
+        <x:v>KB_UPLOAD_READY/04_source_id追溯规则_V50.md</x:v>
       </x:c>
       <x:c r="D8" s="21" t="str">
-        <x:v>publisher/dataset/url/license/覆盖期/版本/sha256/代理/正式状态</x:v>
+        <x:v>source_id字段、完整率、正式使用状态、缺失与冲突处理</x:v>
       </x:c>
       <x:c r="E8" s="21" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>待抽查实例与平台检索复核</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="str"/>
-      <x:c r="H8" s="21" t="str"/>
-      <x:c r="I8" s="21" t="str"/>
+        <x:v>INSTANCE_REVIEW_PENDING</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="str">
+        <x:v>V50-KB04-LOCAL_READY-r1</x:v>
+      </x:c>
+      <x:c r="H8" s="21" t="str">
+        <x:v>6aff15c80eb29f3bb47c3a5bf972bf5e8ccc6cb5dcd7ea65145ae0a133abf3fb</x:v>
+      </x:c>
+      <x:c r="I8" s="21" t="str">
+        <x:v>04_source_id追溯规则_V50.md</x:v>
+      </x:c>
       <x:c r="J8" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="str"/>
-      <x:c r="L8" s="21" t="str"/>
-      <x:c r="M8" s="21" t="str"/>
+      <x:c r="K8" s="21"/>
+      <x:c r="L8" s="21"/>
+      <x:c r="M8" s="21"/>
       <x:c r="N8" s="21" t="str">
-        <x:v>建议用 SRC0721；找不到来源就按缺失处理</x:v>
+        <x:v>规则可上传；索引后抽查SRC0721与空字段行</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
@@ -660,7 +684,7 @@
         <x:v>企业/历史/政策/模拟边界</x:v>
       </x:c>
       <x:c r="C9" s="21" t="str">
-        <x:v>../01_知识库与边界/01_边界词典_V50_草稿.md</x:v>
+        <x:v>KB_UPLOAD_READY/05_企业历史政策模拟边界_V50.md</x:v>
       </x:c>
       <x:c r="D9" s="21" t="str">
         <x:v>企业不越级；历史待核；政策转人工；模拟/代理明示</x:v>
@@ -669,19 +693,25 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>待平台上传后A只读复核</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="str"/>
-      <x:c r="H9" s="21" t="str"/>
-      <x:c r="I9" s="21" t="str"/>
+        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="str">
+        <x:v>V50-KB05-LOCAL_FINAL-r1</x:v>
+      </x:c>
+      <x:c r="H9" s="21" t="str">
+        <x:v>07108849982d83acd4908ac021784ca4eef29858e746385aa2a14472327d306e</x:v>
+      </x:c>
+      <x:c r="I9" s="21" t="str">
+        <x:v>05_企业历史政策模拟边界_V50.md</x:v>
+      </x:c>
       <x:c r="J9" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="str"/>
-      <x:c r="L9" s="21" t="str"/>
-      <x:c r="M9" s="21" t="str"/>
+      <x:c r="K9" s="21"/>
+      <x:c r="L9" s="21"/>
+      <x:c r="M9" s="21"/>
       <x:c r="N9" s="21" t="str">
-        <x:v>该词典是第5类人读主文档，避免双处不一致</x:v>
+        <x:v>人读主文档为01_边界词典_V50.md；导入只用本文件</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -692,7 +722,7 @@
         <x:v>25问基准与判分规范</x:v>
       </x:c>
       <x:c r="C10" s="21" t="str">
-        <x:v>../02_25问基准与判分/02_25问基准框架_V50.xlsx；06_25问判分记录表_V50.xlsx</x:v>
+        <x:v>KB_UPLOAD_READY/06_25问基准判分规范_V50.md</x:v>
       </x:c>
       <x:c r="D10" s="21" t="str">
         <x:v>数值/集合/来源/合规/拒答判分；修一题全25回归</x:v>
@@ -701,19 +731,25 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>待平台上传后A只读复核</x:v>
-      </x:c>
-      <x:c r="G10" s="21" t="str"/>
-      <x:c r="H10" s="21" t="str"/>
-      <x:c r="I10" s="21" t="str"/>
+        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+      </x:c>
+      <x:c r="G10" s="21" t="str">
+        <x:v>V50-KB06-LOCAL_FINAL-r1</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="str">
+        <x:v>49e142c5d3d258b077b74faf59ef381809abd74df6dfaadb13df2812bfa748a8</x:v>
+      </x:c>
+      <x:c r="I10" s="21" t="str">
+        <x:v>06_25问基准判分规范_V50.md</x:v>
+      </x:c>
       <x:c r="J10" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K10" s="21" t="str"/>
-      <x:c r="L10" s="21" t="str"/>
-      <x:c r="M10" s="21" t="str"/>
+      <x:c r="K10" s="21"/>
+      <x:c r="L10" s="21"/>
+      <x:c r="M10" s="21"/>
       <x:c r="N10" s="21" t="str">
-        <x:v>记录模板实际 A:R 共18列；正式实测0/25</x:v>
+        <x:v>正式实测仍为0/25；工作簿模板不直接上传KB</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
@@ -724,33 +760,39 @@
         <x:v>合规声明与正确拒答模板</x:v>
       </x:c>
       <x:c r="C11" s="21" t="str">
-        <x:v>../01_知识库与边界/05_KB知识库7类内容骨架.md#第-7-类合规声明与正确拒答模板-</x:v>
+        <x:v>KB_UPLOAD_READY/07_合规声明与拒答模板_V50.md</x:v>
       </x:c>
       <x:c r="D11" s="21" t="str">
-        <x:v>第一句拒答、缺口、已知边界、合法补证、转人工</x:v>
+        <x:v>第一句拒答、缺口、事实边界、合法补证、转人工</x:v>
       </x:c>
       <x:c r="E11" s="21" t="str">
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>待平台上传后A只读复核</x:v>
-      </x:c>
-      <x:c r="G11" s="21" t="str"/>
-      <x:c r="H11" s="21" t="str"/>
-      <x:c r="I11" s="21" t="str"/>
+        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="str">
+        <x:v>V50-KB07-LOCAL_FINAL-r1</x:v>
+      </x:c>
+      <x:c r="H11" s="21" t="str">
+        <x:v>57d056c7decd91aa4201fef9776c32f43f832c65b659a3b737a2d25d5ff208e6</x:v>
+      </x:c>
+      <x:c r="I11" s="21" t="str">
+        <x:v>07_合规声明与拒答模板_V50.md</x:v>
+      </x:c>
       <x:c r="J11" s="21" t="str">
         <x:v>NOT_UPLOADED</x:v>
       </x:c>
-      <x:c r="K11" s="21" t="str"/>
-      <x:c r="L11" s="21" t="str"/>
-      <x:c r="M11" s="21" t="str"/>
+      <x:c r="K11" s="21"/>
+      <x:c r="L11" s="21"/>
+      <x:c r="M11" s="21"/>
       <x:c r="N11" s="21" t="str">
-        <x:v>不输出制裁/外汇/托管/兑换/利润汇出绕行</x:v>
+        <x:v>推荐第一份导入；不输出监管绕行路径</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="28" t="str">
-        <x:v>上传前逐项补齐：KB版本、SHA-256、平台分段、上传时间、截图路径；七类任一未批准时不得写 KB PASS。</x:v>
+        <x:v>推荐导入顺序：07合规→05边界→02口径→04来源→01模型→03页面→06判分。每个文件索引成功后再传下一个。</x:v>
       </x:c>
       <x:c r="B13" s="29"/>
       <x:c r="C13" s="29"/>
@@ -780,10 +822,10 @@
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="E5:E11">
-      <x:formula1>"LOCAL_FINAL,PARTIAL,BLOCKED,N/A"</x:formula1>
+      <x:formula1>"LOCAL_FINAL,LOCAL_READY"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J5:J11">
-      <x:formula1>"NOT_UPLOADED,UPLOADED / NOT_INDEXED,INDEXED / NOT_TESTED,PASS,FAIL,BLOCKED"</x:formula1>
+      <x:formula1>"NOT_UPLOADED,UPLOAD_IN_PROGRESS,UPLOADED,INDEX_PENDING,INDEXED,INDEX_FAIL,RETRIEVAL_PENDING,RETRIEVAL_PASS,RETRIEVAL_FAIL"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rc34cb1df0ca74fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rce2051c4b7c34dd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,7 +208,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="6">
     <x:dxf>
       <x:font>
         <x:color rgb="FF8A5A00"/>
@@ -226,6 +226,47 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF8A6116"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF4CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF137333"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE6F4EA"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -446,7 +487,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>KB_XH202612_V50_GOVERNANCE｜七类文件清单</x:v>
+        <x:v>KB_XH202612_V50_GOVERNANCE｜七类知识与 CSV 导入清单</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -464,7 +505,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>七类独立导入文件已准备；知识库空对象已创建。当前仍为0文件、未上传、未索引，不代表平台检索或A复核通过。</x:v>
+        <x:v>七个 .md 为维护源；平台只接受 CSV。导入包 KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv 含 7 行文本知识，SHA-256=bb6fc8eb82610b3bbff27ee89fd6f72eebf6152017237dd8afd923cc6b1c9aff。当前空库，尚未导入或检索。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -488,7 +529,7 @@
         <x:v>类别名称</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>权威来源 / 文件</x:v>
+        <x:v>权威来源 / 维护源</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
         <x:v>内容摘要</x:v>
@@ -506,13 +547,13 @@
         <x:v>SHA-256</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>平台文件 / 分段</x:v>
+        <x:v>平台知识标题</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
-        <x:v>上传状态</x:v>
+        <x:v>导入状态</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
-        <x:v>上传时间</x:v>
+        <x:v>导入时间</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
         <x:v>配置截图</x:v>
@@ -550,16 +591,16 @@
         <x:v>446bd1a988c10e82418919a86256423fb74772d7aea212a7224db7d3008db088</x:v>
       </x:c>
       <x:c r="I5" s="20" t="str">
-        <x:v>01_模型与字段绑定说明_V50.md</x:v>
+        <x:v>模型与字段绑定｜模型、表、字段、关系、已知缺口</x:v>
       </x:c>
       <x:c r="J5" s="20" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K5" s="20"/>
       <x:c r="L5" s="20"/>
       <x:c r="M5" s="20"/>
       <x:c r="N5" s="20" t="str">
-        <x:v>文件已可上传；不得写成A04最终冻结或上游已批准</x:v>
+        <x:v>维护源可用；通过 CSV 第1行导入。不得写成A04最终冻结或上游已批准</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -579,7 +620,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F6" s="21" t="str">
-        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G6" s="21" t="str">
         <x:v>V50-KB02-LOCAL_FINAL-r1</x:v>
@@ -588,16 +629,16 @@
         <x:v>0fa0f8359ccf6135a1605a6809136da846e4d5d0908818fbdd2ea3c71b6147fe</x:v>
       </x:c>
       <x:c r="I6" s="21" t="str">
-        <x:v>02_指标公式空值日期口径_V50.md</x:v>
+        <x:v>指标公式与口径｜汇率、通胀、空值、日期、单位</x:v>
       </x:c>
       <x:c r="J6" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K6" s="21"/>
       <x:c r="L6" s="21"/>
       <x:c r="M6" s="21"/>
       <x:c r="N6" s="21" t="str">
-        <x:v>B自有内容本地定稿；平台上传和检索尚未开始</x:v>
+        <x:v>B自有内容本地定稿；CSV导入和检索尚未开始</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" customHeight="1">
@@ -626,10 +667,10 @@
         <x:v>3452c3fbcde1cd6589fe05f655cd9a8f91c3d90c7ce32b0b76f8649f21591c07</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
-        <x:v>03_六页页面说明_V50.md</x:v>
+        <x:v>DB01—DB06 六页说明｜页面、筛选器、联动、验收状态</x:v>
       </x:c>
       <x:c r="J7" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K7" s="21"/>
       <x:c r="L7" s="21"/>
@@ -664,16 +705,16 @@
         <x:v>6aff15c80eb29f3bb47c3a5bf972bf5e8ccc6cb5dcd7ea65145ae0a133abf3fb</x:v>
       </x:c>
       <x:c r="I8" s="21" t="str">
-        <x:v>04_source_id追溯规则_V50.md</x:v>
+        <x:v>source_id 追溯｜来源、许可、哈希、观测期、质量</x:v>
       </x:c>
       <x:c r="J8" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K8" s="21"/>
       <x:c r="L8" s="21"/>
       <x:c r="M8" s="21"/>
       <x:c r="N8" s="21" t="str">
-        <x:v>规则可上传；索引后抽查SRC0721与空字段行</x:v>
+        <x:v>规则已进入CSV第4行；导入后抽查SRC0721与空字段行</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
@@ -693,7 +734,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>V50-KB05-LOCAL_FINAL-r1</x:v>
@@ -702,16 +743,16 @@
         <x:v>07108849982d83acd4908ac021784ca4eef29858e746385aa2a14472327d306e</x:v>
       </x:c>
       <x:c r="I9" s="21" t="str">
-        <x:v>05_企业历史政策模拟边界_V50.md</x:v>
+        <x:v>企业历史政策模拟边界｜披露、1970、pending、代理、情景</x:v>
       </x:c>
       <x:c r="J9" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K9" s="21"/>
       <x:c r="L9" s="21"/>
       <x:c r="M9" s="21"/>
       <x:c r="N9" s="21" t="str">
-        <x:v>人读主文档为01_边界词典_V50.md；导入只用本文件</x:v>
+        <x:v>人读主文档为01_边界词典_V50.md；平台使用CSV第5行</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -731,7 +772,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>V50-KB06-LOCAL_FINAL-r1</x:v>
@@ -740,16 +781,16 @@
         <x:v>49e142c5d3d258b077b74faf59ef381809abd74df6dfaadb13df2812bfa748a8</x:v>
       </x:c>
       <x:c r="I10" s="21" t="str">
-        <x:v>06_25问基准判分规范_V50.md</x:v>
+        <x:v>25 问基准与判分｜数值、追溯、拒答、合规、状态</x:v>
       </x:c>
       <x:c r="J10" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K10" s="21"/>
       <x:c r="L10" s="21"/>
       <x:c r="M10" s="21"/>
       <x:c r="N10" s="21" t="str">
-        <x:v>正式实测仍为0/25；工作簿模板不直接上传KB</x:v>
+        <x:v>正式实测仍为0/25；工作簿模板不直接导入KB</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
@@ -769,7 +810,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>PLATFORM_UPLOAD_AND_A_REVIEW_PENDING</x:v>
+        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>V50-KB07-LOCAL_FINAL-r1</x:v>
@@ -778,21 +819,21 @@
         <x:v>57d056c7decd91aa4201fef9776c32f43f832c65b659a3b737a2d25d5ff208e6</x:v>
       </x:c>
       <x:c r="I11" s="21" t="str">
-        <x:v>07_合规声明与拒答模板_V50.md</x:v>
+        <x:v>合规声明与拒答｜制裁、外汇、托管、兑换、人工复核</x:v>
       </x:c>
       <x:c r="J11" s="21" t="str">
-        <x:v>NOT_UPLOADED</x:v>
+        <x:v>NOT_IMPORTED</x:v>
       </x:c>
       <x:c r="K11" s="21"/>
       <x:c r="L11" s="21"/>
       <x:c r="M11" s="21"/>
       <x:c r="N11" s="21" t="str">
-        <x:v>推荐第一份导入；不输出监管绕行路径</x:v>
+        <x:v>CSV第7行；不输出监管绕行路径</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="28" t="str">
-        <x:v>推荐导入顺序：07合规→05边界→02口径→04来源→01模型→03页面→06判分。每个文件索引成功后再传下一个。</x:v>
+        <x:v>唯一平台导入文件：KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv。一次导入7条文本知识，禁止逐个选择 .md；导入后先核对7条标题/版本，再执行7/7向量库检索。</x:v>
       </x:c>
       <x:c r="B13" s="29"/>
       <x:c r="C13" s="29"/>
@@ -818,14 +859,17 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PARTIAL"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="J5:J11">
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="NOT_"/>
+    <x:cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="NOT_IMPORTED"/>
+    <x:cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="IMPORT_FAIL"/>
+    <x:cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="IMPORTED"/>
+    <x:cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="RETRIEVAL_PASS"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="E5:E11">
       <x:formula1>"LOCAL_FINAL,LOCAL_READY"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J5:J11">
-      <x:formula1>"NOT_UPLOADED,UPLOAD_IN_PROGRESS,UPLOADED,INDEX_PENDING,INDEXED,INDEX_FAIL,RETRIEVAL_PENDING,RETRIEVAL_PASS,RETRIEVAL_FAIL"</x:formula1>
+      <x:formula1>"NOT_IMPORTED,IMPORTED,IMPORT_FAIL,RETRIEVAL_PASS,RETRIEVAL_FAIL"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/KB_FILE_MANIFEST_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rce2051c4b7c34dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB文件清单" sheetId="1" r:id="Rb433de357c50441e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -234,7 +234,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -245,7 +245,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -255,7 +255,7 @@
         <x:color rgb="FF8A6116"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4CE"/>
         </x:patternFill>
       </x:fill>
@@ -265,7 +265,7 @@
         <x:color rgb="FF137333"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE6F4EA"/>
         </x:patternFill>
       </x:fill>
@@ -503,9 +503,9 @@
       <x:c r="M1" s="4"/>
       <x:c r="N1" s="4"/>
     </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>七个 .md 为维护源；平台只接受 CSV。导入包 KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv 含 7 行文本知识，SHA-256=bb6fc8eb82610b3bbff27ee89fd6f72eebf6152017237dd8afd923cc6b1c9aff。当前空库，尚未导入或检索。</x:v>
+        <x:v>七个 .md 为维护源；正式平台知识共43条，全部启用并逐行重新保存触发重索引，正式7类向量检索7/7 PASS；initial_import_sha256=5de78eea5d88f8d5d7cb3bfb3e0f3bc899e755c26ed58cc6834c8bcdfa29167c；current_synced_source_sha256=f9b98523b9c4f7d0c89e97cfd60ce4d14eb837209004a14c5b697dc09215b022；当前SMOKE_5_OF_5 / AI04_PASS / AI06_PASS / AI22_PASS / AI17_PASS / AI18_PASS；FORMAL_25Q_25_OF_25；禁止重复导入</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -565,7 +565,7 @@
         <x:v>备注 / 阻塞项</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="70" customHeight="1">
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
       <x:c r="A5" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -582,7 +582,7 @@
         <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>UPSTREAM_SIGN_PENDING / A最终冻结与签收待补</x:v>
+        <x:v>UPSTREAM_SIGN_PENDING / RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
         <x:v>V50-KB01-LOCAL_READY-r1</x:v>
@@ -591,19 +591,25 @@
         <x:v>446bd1a988c10e82418919a86256423fb74772d7aea212a7224db7d3008db088</x:v>
       </x:c>
       <x:c r="I5" s="20" t="str">
-        <x:v>模型与字段绑定｜模型、表、字段、关系、已知缺口</x:v>
+        <x:v>模型与字段绑定说明-1…5（5条）</x:v>
       </x:c>
       <x:c r="J5" s="20" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K5" s="20"/>
-      <x:c r="L5" s="20"/>
-      <x:c r="M5" s="20"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L5" s="20" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_07_模型检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M5" s="20" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N5" s="20" t="str">
-        <x:v>维护源可用；通过 CSV 第1行导入。不得写成A04最终冻结或上游已批准</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="70" customHeight="1">
+        <x:v>维护源可用；本类已拆分导入5条。不得写成A04最终冻结或上游已批准。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -620,7 +626,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F6" s="21" t="str">
-        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
+        <x:v>RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G6" s="21" t="str">
         <x:v>V50-KB02-LOCAL_FINAL-r1</x:v>
@@ -629,19 +635,25 @@
         <x:v>0fa0f8359ccf6135a1605a6809136da846e4d5d0908818fbdd2ea3c71b6147fe</x:v>
       </x:c>
       <x:c r="I6" s="21" t="str">
-        <x:v>指标公式与口径｜汇率、通胀、空值、日期、单位</x:v>
+        <x:v>指标公式与口径-1…5（5条）</x:v>
       </x:c>
       <x:c r="J6" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K6" s="21"/>
-      <x:c r="L6" s="21"/>
-      <x:c r="M6" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K6" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L6" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_08_口径检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M6" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N6" s="21" t="str">
-        <x:v>B自有内容本地定稿；CSV导入和检索尚未开始</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="70" customHeight="1">
+        <x:v>B自有内容本地定稿；本类已拆分导入5条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -658,7 +670,7 @@
         <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>PAGE_EVIDENCE_AND_G3_SIGN_PENDING</x:v>
+        <x:v>PAGE_EVIDENCE_AND_G3_SIGN_PENDING / RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
         <x:v>V50-KB03-LOCAL_READY-r2</x:v>
@@ -667,19 +679,25 @@
         <x:v>3452c3fbcde1cd6589fe05f655cd9a8f91c3d90c7ce32b0b76f8649f21591c07</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
-        <x:v>DB01—DB06 六页说明｜页面、筛选器、联动、验收状态</x:v>
+        <x:v>六页页面说明-1…8（8条）</x:v>
       </x:c>
       <x:c r="J7" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K7" s="21"/>
-      <x:c r="L7" s="21"/>
-      <x:c r="M7" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K7" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L7" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_09_页面检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M7" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N7" s="21" t="str">
-        <x:v>DB01/DB02 B复核通过、DB06正式PASS；DB04格式收口/B正式复核与G3待完成</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="70" customHeight="1">
+        <x:v>DB01/DB02 B复核通过、DB06正式PASS；DB04格式收口/B正式复核与G3待完成；本类已拆分导入8条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -696,7 +714,7 @@
         <x:v>LOCAL_READY</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>INSTANCE_REVIEW_PENDING</x:v>
+        <x:v>INSTANCE_REVIEW_PENDING / RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
         <x:v>V50-KB04-LOCAL_READY-r1</x:v>
@@ -705,19 +723,25 @@
         <x:v>6aff15c80eb29f3bb47c3a5bf972bf5e8ccc6cb5dcd7ea65145ae0a133abf3fb</x:v>
       </x:c>
       <x:c r="I8" s="21" t="str">
-        <x:v>source_id 追溯｜来源、许可、哈希、观测期、质量</x:v>
+        <x:v>source_id追溯规则-1…6（6条）</x:v>
       </x:c>
       <x:c r="J8" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K8" s="21"/>
-      <x:c r="L8" s="21"/>
-      <x:c r="M8" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L8" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_10_来源检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N8" s="21" t="str">
-        <x:v>规则已进入CSV第4行；导入后抽查SRC0721与空字段行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="70" customHeight="1">
+        <x:v>source_id规则已进入正式拆分CSV；本类已拆分导入6条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -734,7 +758,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
+        <x:v>RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>V50-KB05-LOCAL_FINAL-r1</x:v>
@@ -743,19 +767,25 @@
         <x:v>07108849982d83acd4908ac021784ca4eef29858e746385aa2a14472327d306e</x:v>
       </x:c>
       <x:c r="I9" s="21" t="str">
-        <x:v>企业历史政策模拟边界｜披露、1970、pending、代理、情景</x:v>
+        <x:v>企业历史政策模拟边界-1…5（5条）</x:v>
       </x:c>
       <x:c r="J9" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K9" s="21"/>
-      <x:c r="L9" s="21"/>
-      <x:c r="M9" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L9" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_11_边界检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N9" s="21" t="str">
-        <x:v>人读主文档为01_边界词典_V50.md；平台使用CSV第5行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="70" customHeight="1">
+        <x:v>人读主文档为01_边界词典_V50.md；本类已拆分导入5条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -772,7 +802,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
+        <x:v>RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>V50-KB06-LOCAL_FINAL-r1</x:v>
@@ -781,19 +811,25 @@
         <x:v>49e142c5d3d258b077b74faf59ef381809abd74df6dfaadb13df2812bfa748a8</x:v>
       </x:c>
       <x:c r="I10" s="21" t="str">
-        <x:v>25 问基准与判分｜数值、追溯、拒答、合规、状态</x:v>
+        <x:v>25问基准判分规范-1…5（5条）</x:v>
       </x:c>
       <x:c r="J10" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K10" s="21"/>
-      <x:c r="L10" s="21"/>
-      <x:c r="M10" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K10" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L10" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_12_25问检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M10" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N10" s="21" t="str">
-        <x:v>正式实测仍为0/25；工作簿模板不直接导入KB</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="70" customHeight="1">
+        <x:v>正式25问已记录25/25（PASS 8，BLOCKED 17）；工作簿模板不直接导入KB；本类已拆分导入5条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -810,7 +846,7 @@
         <x:v>LOCAL_FINAL</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>PLATFORM_IMPORT_AND_A_REVIEW_PENDING</x:v>
+        <x:v>RETRIEVAL_PASS / A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>V50-KB07-LOCAL_FINAL-r1</x:v>
@@ -819,21 +855,27 @@
         <x:v>57d056c7decd91aa4201fef9776c32f43f832c65b659a3b737a2d25d5ff208e6</x:v>
       </x:c>
       <x:c r="I11" s="21" t="str">
-        <x:v>合规声明与拒答｜制裁、外汇、托管、兑换、人工复核</x:v>
+        <x:v>合规声明与拒答模板-1…9（9条）</x:v>
       </x:c>
       <x:c r="J11" s="21" t="str">
-        <x:v>NOT_IMPORTED</x:v>
-      </x:c>
-      <x:c r="K11" s="21"/>
-      <x:c r="L11" s="21"/>
-      <x:c r="M11" s="21"/>
+        <x:v>IMPORTED / ENABLED / RETRIEVAL_PASS</x:v>
+      </x:c>
+      <x:c r="K11" s="21" t="str">
+        <x:v>2026-08-31（精确导入时间待补）</x:v>
+      </x:c>
+      <x:c r="L11" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02/05/06 检索失败截图；证据/B04_20260831/B04_13_合规检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="M11" s="21" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
       <x:c r="N11" s="21" t="str">
-        <x:v>CSV第7行；不输出监管绕行路径</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>不输出监管绕行路径；本类已拆分导入9条。43条逐行重新保存触发重索引；本类向量检索PASS，正式7类合计7/7。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="28" t="str">
-        <x:v>唯一平台导入文件：KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv。一次导入7条文本知识，禁止逐个选择 .md；导入后先核对7条标题/版本，再执行7/7向量库检索。</x:v>
+        <x:v>当前正式导入包仍为 05_工具脚本/kb_csv_out/ALL_IN_IMPORT_ORDER.csv，共43条（5+5+8+6+5+5+9），PLAIN / ENABLE / V1。旧7行CSV继续标记SUPERSEDED / DO_NOT_REIMPORT。KB逐行重存重索引后7类检索7/7 PASS。下一步：A只读复核；A未实际复核前不得写B04正式PASS或最终冻结。当前SMOKE_5_OF_5 / AI04_PASS / AI06_PASS / AI22_PASS / AI17_PASS / AI18_PASS，FORMAL_25Q_25_OF_25。</x:v>
       </x:c>
       <x:c r="B13" s="29"/>
       <x:c r="C13" s="29"/>
